--- a/pagina/data/informe_lgtbi.xlsx
+++ b/pagina/data/informe_lgtbi.xlsx
@@ -14,10 +14,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Historico_mensual" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Categorias'!$A$1:$E$49</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regiones'!$A$1:$C$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Categorias'!$A$1:$E$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Regiones'!$A$1:$C$18</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Sexo_edad'!$A$1:$E$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Historico_mensual'!$A$1:$D$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Historico_mensual'!$A$1:$D$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -38,6 +38,9 @@
     </font>
     <font>
       <b val="1"/>
+    </font>
+    <font>
+      <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
@@ -48,9 +51,6 @@
     <font>
       <i val="1"/>
       <color rgb="00595959"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <i val="1"/>
@@ -71,13 +71,19 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
+    </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
     <border>
       <left style="thin">
@@ -99,22 +105,22 @@
   </cellStyleXfs>
   <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -497,7 +503,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Centro Emergencia Mujer y Familia · Enero - Julio 2026 (preliminar)</t>
+          <t>Centro Emergencia Mujer y Familia · Enero - Agosto 2026 (preliminar)</t>
         </is>
       </c>
     </row>
@@ -508,7 +514,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
     </row>
     <row r="5">
@@ -528,7 +534,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7">
@@ -538,7 +544,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="9">
@@ -549,7 +555,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>2026-08-18 10:33</t>
+          <t>2026-09-18 09:54</t>
         </is>
       </c>
     </row>
@@ -568,7 +574,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E49"/>
+  <dimension ref="A1:E50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -622,10 +628,10 @@
         </is>
       </c>
       <c r="D2" s="9" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E2" s="10" t="n">
-        <v>80.59999999999999</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3">
@@ -645,10 +651,10 @@
         </is>
       </c>
       <c r="D3" s="9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" s="10" t="n">
-        <v>19.4</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -668,10 +674,10 @@
         </is>
       </c>
       <c r="D4" s="9" t="n">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="E4" s="10" t="n">
-        <v>91.7</v>
+        <v>92.5</v>
       </c>
     </row>
     <row r="5">
@@ -694,7 +700,7 @@
         <v>3</v>
       </c>
       <c r="E5" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="6">
@@ -714,10 +720,10 @@
         </is>
       </c>
       <c r="D6" s="9" t="n">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="E6" s="10" t="n">
-        <v>97.2</v>
+        <v>97.5</v>
       </c>
     </row>
     <row r="7">
@@ -740,7 +746,7 @@
         <v>1</v>
       </c>
       <c r="E7" s="10" t="n">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="8">
@@ -760,10 +766,10 @@
         </is>
       </c>
       <c r="D8" s="9" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E8" s="10" t="n">
-        <v>58.3</v>
+        <v>57.5</v>
       </c>
     </row>
     <row r="9">
@@ -783,10 +789,10 @@
         </is>
       </c>
       <c r="D9" s="9" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E9" s="10" t="n">
-        <v>41.7</v>
+        <v>42.5</v>
       </c>
     </row>
     <row r="10">
@@ -806,10 +812,10 @@
         </is>
       </c>
       <c r="D10" s="9" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E10" s="10" t="n">
-        <v>52.8</v>
+        <v>52.5</v>
       </c>
     </row>
     <row r="11">
@@ -829,10 +835,10 @@
         </is>
       </c>
       <c r="D11" s="9" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E11" s="10" t="n">
-        <v>36.1</v>
+        <v>37.5</v>
       </c>
     </row>
     <row r="12">
@@ -855,7 +861,7 @@
         <v>4</v>
       </c>
       <c r="E12" s="10" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="13">
@@ -875,10 +881,10 @@
         </is>
       </c>
       <c r="D13" s="9" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E13" s="10" t="n">
-        <v>58.3</v>
+        <v>60</v>
       </c>
     </row>
     <row r="14">
@@ -901,7 +907,7 @@
         <v>10</v>
       </c>
       <c r="E14" s="10" t="n">
-        <v>27.8</v>
+        <v>25</v>
       </c>
     </row>
     <row r="15">
@@ -924,7 +930,7 @@
         <v>2</v>
       </c>
       <c r="E15" s="10" t="n">
-        <v>5.6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -935,19 +941,19 @@
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>identidad_genero</t>
+          <t>orientacion_sexual</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>Ninguno</t>
+          <t>Pansexual</t>
         </is>
       </c>
       <c r="D16" s="9" t="n">
-        <v>18</v>
+        <v>1</v>
       </c>
       <c r="E16" s="10" t="n">
-        <v>50</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="17">
@@ -963,14 +969,14 @@
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>Cisgénero</t>
+          <t>Ninguno</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="E17" s="10" t="n">
-        <v>19.4</v>
+        <v>47.5</v>
       </c>
     </row>
     <row r="18">
@@ -986,14 +992,14 @@
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>Mujer trans</t>
+          <t>Cisgénero</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E18" s="10" t="n">
-        <v>13.9</v>
+        <v>22.5</v>
       </c>
     </row>
     <row r="19">
@@ -1009,14 +1015,14 @@
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>Género no binario</t>
+          <t>Mujer trans</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E19" s="10" t="n">
-        <v>8.300000000000001</v>
+        <v>15</v>
       </c>
     </row>
     <row r="20">
@@ -1032,14 +1038,14 @@
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>Transexual</t>
+          <t>Género no binario</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" s="10" t="n">
-        <v>2.8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="21">
@@ -1050,19 +1056,19 @@
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>intersexual</t>
+          <t>identidad_genero</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
         <is>
-          <t>No intersexual</t>
+          <t>Transexual</t>
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="E21" s="10" t="n">
-        <v>86.09999999999999</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="22">
@@ -1073,19 +1079,19 @@
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>tipo_violencia</t>
+          <t>intersexual</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>Psicológica</t>
+          <t>No intersexual</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="E22" s="10" t="n">
-        <v>41.7</v>
+        <v>87.5</v>
       </c>
     </row>
     <row r="23">
@@ -1101,14 +1107,14 @@
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>Sexual</t>
+          <t>Psicológica</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="E23" s="10" t="n">
-        <v>33.3</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24">
@@ -1124,37 +1130,37 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>Física</t>
+          <t>Sexual</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E24" s="10" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>mujeres</t>
+          <t>hombres</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>edad</t>
+          <t>tipo_violencia</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>18 a 59 años</t>
+          <t>Física</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>48</v>
+        <v>10</v>
       </c>
       <c r="E25" s="10" t="n">
-        <v>78.7</v>
+        <v>25</v>
       </c>
     </row>
     <row r="26">
@@ -1170,14 +1176,14 @@
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>0 a 17 años</t>
+          <t>18 a 59 años</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>13</v>
+        <v>55</v>
       </c>
       <c r="E26" s="10" t="n">
-        <v>21.3</v>
+        <v>80.90000000000001</v>
       </c>
     </row>
     <row r="27">
@@ -1188,19 +1194,19 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>discapacidad</t>
+          <t>edad</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>0 a 17 años</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>59</v>
+        <v>13</v>
       </c>
       <c r="E27" s="10" t="n">
-        <v>96.7</v>
+        <v>19.1</v>
       </c>
     </row>
     <row r="28">
@@ -1216,14 +1222,14 @@
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>2</v>
+        <v>66</v>
       </c>
       <c r="E28" s="10" t="n">
-        <v>3.3</v>
+        <v>97.09999999999999</v>
       </c>
     </row>
     <row r="29">
@@ -1234,19 +1240,19 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>extranjero</t>
+          <t>discapacidad</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>54</v>
+        <v>2</v>
       </c>
       <c r="E29" s="10" t="n">
-        <v>88.5</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="30">
@@ -1262,14 +1268,14 @@
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>7</v>
+        <v>61</v>
       </c>
       <c r="E30" s="10" t="n">
-        <v>11.5</v>
+        <v>89.7</v>
       </c>
     </row>
     <row r="31">
@@ -1280,19 +1286,19 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>trabaja</t>
+          <t>extranjero</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>33</v>
+        <v>7</v>
       </c>
       <c r="E31" s="10" t="n">
-        <v>54.1</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="32">
@@ -1308,14 +1314,14 @@
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>No</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E32" s="10" t="n">
-        <v>45.9</v>
+        <v>52.9</v>
       </c>
     </row>
     <row r="33">
@@ -1326,19 +1332,19 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>nivel_riesgo</t>
+          <t>trabaja</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>Moderado</t>
+          <t>Si</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E33" s="10" t="n">
-        <v>47.5</v>
+        <v>47.1</v>
       </c>
     </row>
     <row r="34">
@@ -1354,14 +1360,14 @@
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>Leve</t>
+          <t>Moderado</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="E34" s="10" t="n">
-        <v>29.5</v>
+        <v>44.1</v>
       </c>
     </row>
     <row r="35">
@@ -1377,14 +1383,14 @@
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>Severo</t>
+          <t>Leve</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="E35" s="10" t="n">
-        <v>23</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="36">
@@ -1395,19 +1401,19 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>orientacion_sexual</t>
+          <t>nivel_riesgo</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>Lesbiana</t>
+          <t>Severo</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>34</v>
+        <v>18</v>
       </c>
       <c r="E36" s="10" t="n">
-        <v>55.7</v>
+        <v>26.5</v>
       </c>
     </row>
     <row r="37">
@@ -1423,14 +1429,14 @@
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>Bisexual</t>
+          <t>Lesbiana</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="E37" s="10" t="n">
-        <v>36.1</v>
+        <v>55.9</v>
       </c>
     </row>
     <row r="38">
@@ -1446,14 +1452,14 @@
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>Heterosexual</t>
+          <t>Bisexual</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>3</v>
+        <v>23</v>
       </c>
       <c r="E38" s="10" t="n">
-        <v>4.9</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="39">
@@ -1469,14 +1475,14 @@
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>Pansexual</t>
+          <t>Heterosexual</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E39" s="10" t="n">
-        <v>1.6</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="40">
@@ -1492,14 +1498,14 @@
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>Asexual</t>
+          <t>Pansexual</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
         <v>1</v>
       </c>
       <c r="E40" s="10" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="41">
@@ -1510,19 +1516,19 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>identidad_genero</t>
+          <t>orientacion_sexual</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>Ninguno</t>
+          <t>Asexual</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="E41" s="10" t="n">
-        <v>32.8</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="42">
@@ -1538,14 +1544,14 @@
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>Cisgénero</t>
+          <t>Ninguno</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="E42" s="10" t="n">
-        <v>31.1</v>
+        <v>33.8</v>
       </c>
     </row>
     <row r="43">
@@ -1561,14 +1567,14 @@
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>Género no binario</t>
+          <t>Cisgénero</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="E43" s="10" t="n">
-        <v>11.5</v>
+        <v>29.4</v>
       </c>
     </row>
     <row r="44">
@@ -1584,14 +1590,14 @@
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>Hombre trans</t>
+          <t>Género no binario</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E44" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>10.3</v>
       </c>
     </row>
     <row r="45">
@@ -1602,19 +1608,19 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>intersexual</t>
+          <t>identidad_genero</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>No intersexual</t>
+          <t>Hombre trans</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>45</v>
+        <v>6</v>
       </c>
       <c r="E45" s="10" t="n">
-        <v>73.8</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
     <row r="46">
@@ -1630,14 +1636,14 @@
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>Intersexual</t>
+          <t>No intersexual</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>6</v>
+        <v>48</v>
       </c>
       <c r="E46" s="10" t="n">
-        <v>9.800000000000001</v>
+        <v>70.59999999999999</v>
       </c>
     </row>
     <row r="47">
@@ -1648,19 +1654,19 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>tipo_violencia</t>
+          <t>intersexual</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>Física</t>
+          <t>Intersexual</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="E47" s="10" t="n">
-        <v>34.4</v>
+        <v>11.8</v>
       </c>
     </row>
     <row r="48">
@@ -1676,14 +1682,14 @@
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>Sexual</t>
+          <t>Física</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="E48" s="10" t="n">
-        <v>32.8</v>
+        <v>35.3</v>
       </c>
     </row>
     <row r="49">
@@ -1703,14 +1709,37 @@
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E49" s="10" t="n">
-        <v>32.8</v>
+        <v>33.8</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
+        <is>
+          <t>mujeres</t>
+        </is>
+      </c>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>tipo_violencia</t>
+        </is>
+      </c>
+      <c r="C50" s="8" t="inlineStr">
+        <is>
+          <t>Sexual</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="E50" s="10" t="n">
+        <v>30.9</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E49"/>
+  <autoFilter ref="A1:E50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1721,7 +1750,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C17"/>
+  <dimension ref="A1:C18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1753,10 +1782,10 @@
         </is>
       </c>
       <c r="B2" s="9" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="C2" s="10" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3">
@@ -1766,36 +1795,36 @@
         </is>
       </c>
       <c r="B3" s="9" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C3" s="10" t="n">
-        <v>10.3</v>
+        <v>11.1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>CALLAO</t>
+          <t>PIURA</t>
         </is>
       </c>
       <c r="B4" s="9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C4" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>PIURA</t>
+          <t>CALLAO</t>
         </is>
       </c>
       <c r="B5" s="9" t="n">
         <v>8</v>
       </c>
       <c r="C5" s="10" t="n">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="6">
@@ -1808,46 +1837,46 @@
         <v>7</v>
       </c>
       <c r="C6" s="10" t="n">
-        <v>7.2</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t>CUSCO</t>
+          <t>SAN MARTIN</t>
         </is>
       </c>
       <c r="B7" s="9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C7" s="10" t="n">
-        <v>6.2</v>
+        <v>6.5</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>LAMBAYEQUE</t>
+          <t>CUSCO</t>
         </is>
       </c>
       <c r="B8" s="9" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C8" s="10" t="n">
-        <v>4.1</v>
+        <v>5.6</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>SAN MARTIN</t>
+          <t>LAMBAYEQUE</t>
         </is>
       </c>
       <c r="B9" s="9" t="n">
         <v>4</v>
       </c>
       <c r="C9" s="10" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
     </row>
     <row r="10">
@@ -1860,7 +1889,7 @@
         <v>3</v>
       </c>
       <c r="C10" s="10" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="11">
@@ -1873,33 +1902,33 @@
         <v>3</v>
       </c>
       <c r="C11" s="10" t="n">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>CAJAMARCA</t>
+          <t>LA LIBERTAD</t>
         </is>
       </c>
       <c r="B12" s="9" t="n">
         <v>2</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>LA LIBERTAD</t>
+          <t>CAJAMARCA</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
         <v>2</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="14">
@@ -1912,50 +1941,63 @@
         <v>1</v>
       </c>
       <c r="C14" s="10" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>JUNIN</t>
+          <t>PUNO</t>
         </is>
       </c>
       <c r="B15" s="9" t="n">
         <v>1</v>
       </c>
       <c r="C15" s="10" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>ICA</t>
+          <t>JUNIN</t>
         </is>
       </c>
       <c r="B16" s="9" t="n">
         <v>1</v>
       </c>
       <c r="C16" s="10" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>TACNA</t>
+          <t>ICA</t>
         </is>
       </c>
       <c r="B17" s="9" t="n">
         <v>1</v>
       </c>
       <c r="C17" s="10" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>TACNA</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="n">
         <v>1</v>
       </c>
+      <c r="C18" s="10" t="n">
+        <v>0.9</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C17"/>
+  <autoFilter ref="A1:C18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2013,13 +2055,13 @@
         <v>13</v>
       </c>
       <c r="C2" s="8" t="n">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="D2" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E2" s="8" t="n">
-        <v>61</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3">
@@ -2029,16 +2071,16 @@
         </is>
       </c>
       <c r="B3" s="8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C3" s="8" t="n">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="D3" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E3" s="8" t="n">
-        <v>36</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4">
@@ -2048,16 +2090,16 @@
         </is>
       </c>
       <c r="B4" s="8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" s="8" t="n">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="D4" s="8" t="n">
         <v>0</v>
       </c>
       <c r="E4" s="8" t="n">
-        <v>97</v>
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -2072,7 +2114,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2243,8 +2285,28 @@
         <v>14</v>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D8"/>
+  <autoFilter ref="A1:D9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>